--- a/Docx/StaticReviewReport_Design.xlsx
+++ b/Docx/StaticReviewReport_Design.xlsx
@@ -1,44 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmad\Desktop\Computer Enginering\Year 3\Spring 2026\Software Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07C10DB-59E6-43D4-9D4D-31353DC62F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1636543-B94E-4DD3-AA23-699831F64B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectDetails" sheetId="2" r:id="rId1"/>
-    <sheet name="Hospital Class Diagram Review" sheetId="1" r:id="rId2"/>
-    <sheet name="UML Sequence Diagram Review" sheetId="3" r:id="rId3"/>
+    <sheet name="Hospital Class Diagram Revi (2)" sheetId="5" r:id="rId2"/>
+    <sheet name="Hospital Class Diagram Review" sheetId="1" r:id="rId3"/>
+    <sheet name="UML Sequence Diagram Review (2)" sheetId="4" r:id="rId4"/>
+    <sheet name="Initialization Sequence Diagram" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="54">
   <si>
     <t>UML Class Diagram Observation</t>
   </si>
@@ -127,289 +118,742 @@
     <t>FR-IN-01, FR-IN-02</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">While the system shall load all patient records and appointmnets from the JSON file at the startup the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>initialization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> method at  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>HospitalServices</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> call  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>HospitalRepository</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> which is responsible for load, save, and check if the JSON file exist or not. </t>
+    </r>
+  </si>
+  <si>
     <t>PARTIAL, if the JSON file do not exist, the system should intialize empty patient, appointment list. "could be handeled internaly."</t>
   </si>
   <si>
     <t>FR-MM-01</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>HospitalConsole</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> show all the options that shall be disolayed at the Main Menu.</t>
+    </r>
+  </si>
+  <si>
     <t>FR-RP-01 - FR-RP-03</t>
   </si>
   <si>
     <t>FR-SA-01 - FR-SA-04</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">Receptionist </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">select Register Patient from the main menu and then add new patient details, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">HospitalService </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">loades that details to the JSON file by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>HospitalRepository.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>FR-IN-01</t>
+  </si>
+  <si>
+    <t>FR-IN-02</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">HospitalService </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">request appointments from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">HospitalRepository </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">therefore the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>HospitalRepository</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> reads the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>appoinment array from the JSON</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>file</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>and the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> JSON </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>file by appoinments records to the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> HospitalRepository </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>to be presented to the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> HospitalService. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>If the file is missed the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> HospitalRepository </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>reply by empty patient list to the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> HospitalService.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">When the system startup, the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>HospitalService</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> request paitents data from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>HospitalRepository</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> therefore the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>HospitalRepository</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> file reads the patient array from the JSON  and the JSON file reply by paitent records to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">HospitalRepository </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">to present patient to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">HospitalService. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">If the file is missed the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">HospitalRepository </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">reply by empty patient list to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>HospitalService.</t>
+    </r>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High </t>
+  </si>
+  <si>
+    <r>
+      <t>at</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> Initialization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> method at  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>HospitalServices</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> which is resposible load the record from the JSON file at the startup. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>at</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> HospitalConsole</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> show all the options that shall be displayed at the Main Menu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>at</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> HospitalService </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">have method called </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>registerPatient</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> responsible for patient registration which take name, and unique ID.  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>at</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> HospitalService </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>has method called</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve"> scheduleAppoitment </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>which take patient ID, date, and time.                                                   Method is</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t xml:space="preserve">TimeSlotAvailable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>check if the slot available or not.</t>
+    </r>
+  </si>
+  <si>
     <t>FR-VP-01 - FR-VP-03</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">at </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>HospitalService</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> there is a method called </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>getPatients</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> display all patients. Method </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>getAppointmentForPatient</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> which list appointments for each patient by patient ID.</t>
+    </r>
+  </si>
+  <si>
     <t>FR-UP-01 - FR-UP-03</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">at </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>HospitalService</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have method </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+      </rPr>
+      <t>updatePatient</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by getting patient ID and then enter the updated data.</t>
+    </r>
+  </si>
+  <si>
     <t>FR-CA-01 - FR-CA-03</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">at </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>HospitalService</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> there is a method called </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>getPatients</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> display all patients. Method </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>getAppointmentForPatient</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> which list appointments for each patient by patient ID.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>at</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> HospitalService </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>has method called</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> scheduleAppoitment </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>which take patient ID, date, and time.                                                   Method is</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve">TimeSlotAvailable </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>check if the slot available or not.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>at</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> HospitalService </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve">have method called </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>registerPatient</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> responsible for patient registration which take name, and unique ID.  </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>at</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> HospitalConsole</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> show all the options that shall be displayed at the Main Menu.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>at</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t xml:space="preserve"> Initialization</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> method at  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>HospitalServices</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> which is resposible load the record from the JSON file at the startup. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">at </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>HospitalService</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> have method </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-      </rPr>
-      <t>updatePatient</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Google Sans Text"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> by getting patient ID and then enter the updated data.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -698,12 +1142,39 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -722,38 +1193,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -764,7 +1208,14 @@
     <cellStyle name="40% - Accent1" xfId="2" builtinId="31"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="12">
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <border outline="0">
         <top style="medium">
@@ -773,10 +1224,46 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="medium">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="medium">
           <color rgb="FF000000"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FF000000"/>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -851,6 +1338,49 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="medium">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -865,8 +1395,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97C60D9B-1242-41FA-87DD-2702E850220F}" name="Table223" displayName="Table223" ref="A1:E25" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9768572D-DD3B-4AFC-811C-C08A8349B197}" name="Table2235" displayName="Table2235" ref="A1:E25" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1">
   <autoFilter ref="A1:E25" xr:uid="{97C60D9B-1242-41FA-87DD-2702E850220F}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{2F19FAF0-8F0A-4E0D-AB92-398B0E293596}" name="Requirement Reference/ Source"/>
+    <tableColumn id="3" xr3:uid="{B3117416-674F-406A-A789-055B29C8026B}" name="UML Class Diagram Observation"/>
+    <tableColumn id="4" xr3:uid="{B1F2C55F-A492-49B4-AEF0-B7A659E09543}" name="Review Finding / Status"/>
+    <tableColumn id="5" xr3:uid="{B48BCF44-E89E-4BD7-A6B5-6F0A0200849B}" name="Severity"/>
+    <tableColumn id="6" xr3:uid="{2CAB2DA5-E1C0-40A3-939B-05DA8DA1E251}" name="Priority"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{97C60D9B-1242-41FA-87DD-2702E850220F}" name="Table223" displayName="Table223" ref="A1:E23" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
+  <autoFilter ref="A1:E23" xr:uid="{97C60D9B-1242-41FA-87DD-2702E850220F}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{ABFF75A1-57B3-4CB0-9B98-B64AA87C0C25}" name="Requirement Reference/ Source"/>
     <tableColumn id="3" xr3:uid="{4DB69F6B-EE0F-482E-9356-648B2C47FDAF}" name="UML Class Diagram Observation"/>
@@ -878,12 +1422,26 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B14B9B63-BBE4-490C-984C-A2DD390F8FE7}" name="Table22" displayName="Table22" ref="A1:E23" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BFB3CCE4-0CAC-4F85-B959-E9C5DCE6DF21}" name="Table224" displayName="Table224" ref="A1:E23" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="3" tableBorderDxfId="4">
+  <autoFilter ref="A1:E23" xr:uid="{B14B9B63-BBE4-490C-984C-A2DD390F8FE7}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{01DC8BC3-AEDB-4CCB-A725-53E31B3A36D6}" name="Requirement Reference / Source"/>
+    <tableColumn id="3" xr3:uid="{345E69CD-2086-4D44-9971-D6E7456272FA}" name="UML Sequence Diagram Observation"/>
+    <tableColumn id="4" xr3:uid="{F3AA00CC-61FF-4464-9114-AB8941BACAD7}" name="Review Finding / Status"/>
+    <tableColumn id="5" xr3:uid="{3B1187C1-50C8-45AC-BA77-BB16DE7FDCB1}" name="Severity"/>
+    <tableColumn id="6" xr3:uid="{947C37B1-A7E6-4AB8-8673-C8013FB01695}" name="Priority"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B14B9B63-BBE4-490C-984C-A2DD390F8FE7}" name="Table22" displayName="Table22" ref="A1:E23" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A1:E23" xr:uid="{B14B9B63-BBE4-490C-984C-A2DD390F8FE7}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{83C80F16-7122-45C0-925F-4401256F8915}" name="Requirement Reference / Source"/>
-    <tableColumn id="3" xr3:uid="{AA755CD8-7CAF-4141-8C5B-78E595B414F2}" name="UML Sequence Diagram Observation"/>
+    <tableColumn id="3" xr3:uid="{AA755CD8-7CAF-4141-8C5B-78E595B414F2}" name=" "/>
     <tableColumn id="4" xr3:uid="{47E89857-66EA-42A7-890F-D93C5321E9DD}" name="Review Finding / Status"/>
     <tableColumn id="5" xr3:uid="{4E1C6F7A-E735-423A-8317-0F194F983A12}" name="Severity"/>
     <tableColumn id="6" xr3:uid="{2AED8EAC-7442-4CBE-A015-2FE1BBCCA17E}" name="Priority"/>
@@ -1163,109 +1721,109 @@
   <sheetData>
     <row r="1" spans="1:10" ht="21.6" thickBot="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="18"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="25" t="s">
+      <c r="C2" s="29"/>
+      <c r="D2" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="26"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="31"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2"/>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="21">
+      <c r="C3" s="18"/>
+      <c r="D3" s="20">
         <v>1</v>
       </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="21"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2"/>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="22"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2"/>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="24"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2"/>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="29">
+      <c r="C6" s="18"/>
+      <c r="D6" s="19">
         <v>46117</v>
       </c>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="22"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="21"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2"/>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="23" t="s">
+      <c r="C7" s="18"/>
+      <c r="D7" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="24"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="23"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2"/>
@@ -1273,63 +1831,63 @@
         <v>25</v>
       </c>
       <c r="C8" s="12"/>
-      <c r="D8" s="29">
+      <c r="D8" s="19">
         <v>46270</v>
       </c>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="22"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="21"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="23"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="22"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="21"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="24"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="23"/>
     </row>
     <row r="12" spans="1:10" ht="15" thickBot="1">
       <c r="A12" s="2"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="28"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1">
       <c r="A13" s="3"/>
@@ -1345,12 +1903,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B1:J1"/>
@@ -1367,13 +1919,19 @@
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FFF9B7-0693-4E69-91FA-D81C3112730B}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
@@ -1405,11 +1963,11 @@
       <c r="A2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="30" t="s">
-        <v>40</v>
+      <c r="B2" s="13" t="s">
+        <v>44</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>9</v>
@@ -1420,10 +1978,10 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1">
       <c r="A3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>39</v>
+        <v>31</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>11</v>
@@ -1432,11 +1990,11 @@
       <c r="E3" s="9"/>
     </row>
     <row r="4" spans="1:5" ht="66.599999999999994" customHeight="1" thickBot="1">
-      <c r="A4" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>38</v>
+      <c r="A4" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>11</v>
@@ -1446,10 +2004,10 @@
     </row>
     <row r="5" spans="1:5" ht="74.400000000000006" customHeight="1" thickBot="1">
       <c r="A5" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>11</v>
@@ -1459,10 +2017,10 @@
     </row>
     <row r="6" spans="1:5" ht="76.8" customHeight="1" thickBot="1">
       <c r="A6" s="7" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>11</v>
@@ -1472,10 +2030,10 @@
     </row>
     <row r="7" spans="1:5" ht="48" customHeight="1" thickBot="1">
       <c r="A7" s="7" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>11</v>
@@ -1485,10 +2043,10 @@
     </row>
     <row r="8" spans="1:5" ht="45.6" customHeight="1" thickBot="1">
       <c r="A8" s="7" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>11</v>
@@ -1505,6 +2063,200 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="23.5546875" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="28.2" thickBot="1">
+      <c r="A1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="152.4" customHeight="1" thickBot="1">
+      <c r="A2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1">
+      <c r="A3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" spans="1:5" ht="66.599999999999994" customHeight="1" thickBot="1">
+      <c r="A4" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5" spans="1:5" ht="32.4" customHeight="1" thickBot="1">
+      <c r="A5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+    </row>
+    <row r="6" spans="1:5" ht="15" thickBot="1">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6DA32B2-B641-4AC6-97CF-56A9827FB163}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="22.21875" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" customWidth="1"/>
+    <col min="5" max="5" width="33.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="42" thickBot="1">
+      <c r="A1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="53.4" thickBot="1">
+      <c r="A2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="27" thickBot="1">
+      <c r="A3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" spans="1:5" ht="28.2" thickBot="1">
+      <c r="A4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" thickBot="1">
+      <c r="A5" s="7"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+    </row>
+    <row r="6" spans="1:5" ht="15" thickBot="1">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89A790E3-8EA0-4AD3-8961-BC072817172C}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1521,7 +2273,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>1</v>
@@ -1533,35 +2285,39 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="53.4" thickBot="1">
+    <row r="2" spans="1:5" ht="158.4" customHeight="1" thickBot="1">
       <c r="A2" s="7" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="27" thickBot="1">
+    <row r="3" spans="1:5" ht="174.6" customHeight="1" thickBot="1">
       <c r="A3" s="10" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
+      <c r="D3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="28.2" thickBot="1">
       <c r="A4" s="7" t="s">
